--- a/form_bao_gia_cau_hinh_sintech.xlsx
+++ b/form_bao_gia_cau_hinh_sintech.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Truong\Downloads\bao_gia_sintech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6AD59B-54C0-4943-8B81-FB014B2A2FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73B6355-5318-40E5-BCCF-0D2DFBCBC5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53E664AF-38A3-414D-AF72-5AA58059617D}"/>
   </bookViews>
@@ -483,7 +483,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -584,6 +584,51 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -599,53 +644,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1089,107 +1098,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29.45" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" ht="28.15" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="11"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="22.9" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="1:6" ht="27" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="5" spans="1:6" ht="26.45" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="39.75" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="57" t="str">
+        <f ca="1">"SỐ: "&amp;TEXT(NOW(),"hhmmddmmyyyy")&amp;"/BGCH"</f>
+        <v>SỐ: 093805032026/BGCH</v>
+      </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
       <c r="A8" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="53" t="str">
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="47" t="str">
         <f ca="1">CHOOSE(WEEKDAY(TODAY()),"Chủ nhật","Thứ 2","Thứ 3","Thứ 4","Thứ 5","Thứ 6","Thứ 7")&amp; " / " &amp; TEXT(TODAY(),"dd/mm/yyyy")</f>
-        <v>Thứ 2 / 26/01/2026</v>
-      </c>
-      <c r="F8" s="54"/>
+        <v>Thứ 5 / 05/03/2026</v>
+      </c>
+      <c r="F8" s="48"/>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
     </row>
     <row r="10" spans="1:6" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" ht="30.75" customHeight="1">
       <c r="A11" s="27" t="s">
@@ -1220,24 +1232,24 @@
       <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
       <c r="A15" s="30"/>
@@ -1246,18 +1258,18 @@
       <c r="D15" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:6" s="4" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
     </row>
     <row r="17" spans="1:6" ht="21" customHeight="1">
       <c r="A17" s="16" t="s">
@@ -1270,30 +1282,30 @@
       <c r="F17" s="19"/>
     </row>
     <row r="18" spans="1:6" ht="21" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="35"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="21" customHeight="1">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="35"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" ht="21" customHeight="1">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="40"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="24"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -1308,56 +1320,56 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="21" customHeight="1">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="42" t="s">
+      <c r="B22" s="36"/>
+      <c r="C22" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
     </row>
     <row r="23" spans="1:6" ht="21" customHeight="1">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
     </row>
     <row r="25" spans="1:6" ht="21" customHeight="1">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
     </row>
     <row r="26" spans="1:6" ht="21" customHeight="1">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
     </row>
     <row r="27" spans="1:6" ht="21" customHeight="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
     </row>
     <row r="28" spans="1:6" ht="21" customHeight="1">
       <c r="A28" s="9"/>
@@ -1369,6 +1381,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A22:B27"/>
     <mergeCell ref="C22:F27"/>
@@ -1381,15 +1399,9 @@
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
